--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T1_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="77">
   <si>
     <t/>
   </si>
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>62</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.54e+05</t>
-  </si>
-  <si>
-    <t>(79132.426)</t>
-  </si>
-  <si>
-    <t>490.997</t>
-  </si>
-  <si>
-    <t>(37.072)</t>
-  </si>
-  <si>
-    <t>3.657</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>8.254</t>
-  </si>
-  <si>
-    <t>(1.481)</t>
-  </si>
-  <si>
-    <t>87.568</t>
-  </si>
-  <si>
-    <t>(0.516)</t>
-  </si>
-  <si>
-    <t>9.58e+05</t>
-  </si>
-  <si>
-    <t>(59053.489)</t>
-  </si>
-  <si>
-    <t>2.296</t>
-  </si>
-  <si>
-    <t>(0.137)</t>
-  </si>
-  <si>
-    <t>2.857</t>
-  </si>
-  <si>
-    <t>(0.432)</t>
-  </si>
-  <si>
-    <t>31.873</t>
-  </si>
-  <si>
-    <t>(4.169)</t>
-  </si>
-  <si>
-    <t>0.937</t>
-  </si>
-  <si>
-    <t>(0.031)</t>
-  </si>
-  <si>
-    <t>53</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,55 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.86e+05</t>
-  </si>
-  <si>
-    <t>(1.07e+05)</t>
-  </si>
-  <si>
-    <t>494.582</t>
-  </si>
-  <si>
-    <t>(46.534)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
   </si>
   <si>
     <t>3.352</t>
   </si>
   <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>25.264</t>
-  </si>
-  <si>
-    <t>(3.546)</t>
-  </si>
-  <si>
-    <t>91.434</t>
-  </si>
-  <si>
-    <t>(0.382)</t>
-  </si>
-  <si>
-    <t>1.37e+06</t>
-  </si>
-  <si>
-    <t>(58423.296)</t>
-  </si>
-  <si>
-    <t>(0.123)</t>
-  </si>
-  <si>
-    <t>5.943</t>
-  </si>
-  <si>
-    <t>(0.587)</t>
-  </si>
-  <si>
-    <t>43.094</t>
-  </si>
-  <si>
-    <t>(2.923)</t>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -213,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.32e+05</t>
-  </si>
-  <si>
-    <t>3.585</t>
-  </si>
-  <si>
-    <t>-0.305***</t>
-  </si>
-  <si>
-    <t>17.010***</t>
-  </si>
-  <si>
-    <t>3.866***</t>
-  </si>
-  <si>
-    <t>4.12e+05***</t>
-  </si>
-  <si>
-    <t>1.056***</t>
-  </si>
-  <si>
-    <t>3.086***</t>
-  </si>
-  <si>
-    <t>11.221**</t>
-  </si>
-  <si>
-    <t>0.063*</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>
@@ -307,7 +310,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
@@ -330,7 +333,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -353,7 +356,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -373,10 +376,10 @@
         <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -419,10 +422,10 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -465,10 +468,10 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -511,10 +514,10 @@
         <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -557,10 +560,10 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -603,10 +606,10 @@
         <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -646,13 +649,13 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -692,13 +695,13 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -715,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -738,13 +741,13 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -761,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -784,13 +787,13 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -807,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T1_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="76">
   <si>
     <t/>
   </si>
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>63</t>
+  </si>
+  <si>
+    <t>62</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.54e+05</t>
+  </si>
+  <si>
+    <t>(79132.426)</t>
+  </si>
+  <si>
+    <t>490.997</t>
+  </si>
+  <si>
+    <t>(37.072)</t>
+  </si>
+  <si>
+    <t>3.657</t>
+  </si>
+  <si>
+    <t>(0.052)</t>
+  </si>
+  <si>
+    <t>8.254</t>
+  </si>
+  <si>
+    <t>(1.481)</t>
+  </si>
+  <si>
+    <t>87.568</t>
+  </si>
+  <si>
+    <t>(0.516)</t>
+  </si>
+  <si>
+    <t>9.58e+05</t>
+  </si>
+  <si>
+    <t>(59053.489)</t>
+  </si>
+  <si>
+    <t>2.296</t>
+  </si>
+  <si>
+    <t>(0.137)</t>
+  </si>
+  <si>
+    <t>2.857</t>
+  </si>
+  <si>
+    <t>(0.432)</t>
+  </si>
+  <si>
+    <t>31.873</t>
+  </si>
+  <si>
+    <t>(4.169)</t>
+  </si>
+  <si>
+    <t>0.937</t>
+  </si>
+  <si>
+    <t>(0.031)</t>
+  </si>
+  <si>
+    <t>53</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,55 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
+    <t>6.86e+05</t>
+  </si>
+  <si>
+    <t>(1.07e+05)</t>
+  </si>
+  <si>
+    <t>494.582</t>
+  </si>
+  <si>
+    <t>(46.534)</t>
   </si>
   <si>
     <t>3.352</t>
   </si>
   <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>25.264</t>
+  </si>
+  <si>
+    <t>(3.546)</t>
+  </si>
+  <si>
+    <t>91.434</t>
+  </si>
+  <si>
+    <t>(0.382)</t>
+  </si>
+  <si>
+    <t>1.37e+06</t>
+  </si>
+  <si>
+    <t>(58423.296)</t>
+  </si>
+  <si>
+    <t>(0.123)</t>
+  </si>
+  <si>
+    <t>5.943</t>
+  </si>
+  <si>
+    <t>(0.587)</t>
+  </si>
+  <si>
+    <t>43.094</t>
+  </si>
+  <si>
+    <t>(2.923)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +213,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.32e+05</t>
+  </si>
+  <si>
+    <t>3.585</t>
+  </si>
+  <si>
+    <t>-0.305***</t>
+  </si>
+  <si>
+    <t>17.010***</t>
+  </si>
+  <si>
+    <t>3.866***</t>
+  </si>
+  <si>
+    <t>4.12e+05***</t>
+  </si>
+  <si>
+    <t>1.056***</t>
+  </si>
+  <si>
+    <t>3.086***</t>
+  </si>
+  <si>
+    <t>11.221**</t>
+  </si>
+  <si>
+    <t>0.063*</t>
   </si>
 </sst>
 </file>
@@ -310,7 +307,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
@@ -333,7 +330,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -356,7 +353,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -376,10 +373,10 @@
         <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -422,10 +419,10 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -468,10 +465,10 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -514,10 +511,10 @@
         <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -560,10 +557,10 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -606,10 +603,10 @@
         <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -649,13 +646,13 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -672,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -695,13 +692,13 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -718,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -741,13 +738,13 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
@@ -764,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -787,13 +784,13 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
@@ -810,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
